--- a/registered_users.xlsx
+++ b/registered_users.xlsx
@@ -113,37 +113,37 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="0">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t>كريم محمود</t>
+          <t>سعيد عثمان</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="0">
         <is>
-          <t>كريم</t>
+          <t>سعيد</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="0">
         <is>
-          <t>محمود</t>
+          <t>عثمان</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="0">
         <is>
-          <t>01025556677</t>
+          <t>01044445555</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="0">
         <is>
-          <t>kareem@gmail.com</t>
+          <t>saeed@gmail.com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr" s="0">
         <is>
-          <t>الجيزة - الدقي شارع التحرير</t>
+          <t>طنطا</t>
         </is>
       </c>
       <c r="H2" t="inlineStr" s="0">
@@ -163,49 +163,49 @@
       </c>
       <c r="K2" t="inlineStr" s="0">
         <is>
-          <t>2026-10-20 17:22:15</t>
+          <t>2026-10-20 18:08:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="0">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="0">
         <is>
-          <t>مدير المحطة</t>
+          <t>خالد احمد</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="0">
         <is>
-          <t>مدير</t>
+          <t>خالد</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="0">
         <is>
-          <t>المحطة</t>
+          <t>احمد</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="0">
         <is>
-          <t>01000000000</t>
+          <t>01009170600</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="0">
         <is>
-          <t>admin@station.com</t>
+          <t>jihadhamed55@gmail.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr" s="0">
         <is>
-          <t>مكتب إدارة محطة رمسيس</t>
+          <t>دمياط كفر سعد الشارع الجديد</t>
         </is>
       </c>
       <c r="H3" t="inlineStr" s="0">
         <is>
-          <t>مدير المحطة</t>
+          <t>عميل مسافر</t>
         </is>
       </c>
       <c r="I3" t="inlineStr" s="0">
@@ -220,49 +220,49 @@
       </c>
       <c r="K3" t="inlineStr" s="0">
         <is>
-          <t>2026-10-20 15:42:07</t>
+          <t>2026-10-20 18:02:05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="0">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="0">
         <is>
-          <t>Mohamed Ahmed</t>
+          <t>مدير المحطة</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="0">
         <is>
-          <t>Mohamed</t>
+          <t>مدير</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="0">
         <is>
-          <t>Ahmed</t>
+          <t>المحطة</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="0">
         <is>
-          <t>01009170604</t>
+          <t>01000000000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="0">
         <is>
-          <t>jihadhamed42@gmail.com</t>
+          <t>admin@station.com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr" s="0">
         <is>
-          <t>دمياط تفتيش كفر سعد كفر سليمان البحرى</t>
+          <t>مكتب إدارة محطة رمسيس</t>
         </is>
       </c>
       <c r="H4" t="inlineStr" s="0">
         <is>
-          <t>عميل مسافر</t>
+          <t>مدير المحطة</t>
         </is>
       </c>
       <c r="I4" t="inlineStr" s="0">
@@ -277,62 +277,119 @@
       </c>
       <c r="K4" t="inlineStr" s="0">
         <is>
-          <t>2026-10-19 18:35:34</t>
+          <t>2026-10-20 15:42:07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="0">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="0">
+        <is>
+          <t>Mohamed Ahmed</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="0">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="0">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="0">
+        <is>
+          <t>01009170604</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr" s="0">
+        <is>
+          <t>jihadhamed42@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr" s="0">
+        <is>
+          <t>دمياط تفتيش كفر سعد كفر سليمان البحرى</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr" s="0">
+        <is>
+          <t>عميل مسافر</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr" s="0">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr" s="0">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr" s="0">
+        <is>
+          <t>2026-10-19 18:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="0">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr" s="0">
+      <c r="B6" t="inlineStr" s="0">
         <is>
           <t>Jihad Hamed</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr" s="0">
+      <c r="C6" t="inlineStr" s="0">
         <is>
           <t>Jihad</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr" s="0">
+      <c r="D6" t="inlineStr" s="0">
         <is>
           <t>Hamed</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr" s="0">
+      <c r="E6" t="inlineStr" s="0">
         <is>
           <t>01093679541</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr" s="0">
+      <c r="F6" t="inlineStr" s="0">
         <is>
           <t>jihadhamed027@gmail.com</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr" s="0">
+      <c r="G6" t="inlineStr" s="0">
         <is>
           <t>دمياط تفتيش كفر سعد كفر سليمان البحرى</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr" s="0">
+      <c r="H6" t="inlineStr" s="0">
         <is>
           <t>عميل مسافر</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr" s="0">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr" s="0">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr" s="0">
+      <c r="I6" t="inlineStr" s="0">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr" s="0">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr" s="0">
         <is>
           <t>2026-10-19 17:41:12</t>
         </is>
